--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/VIRGINIA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/VIRGINIA_2015.xlsx
@@ -823,7 +823,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="27">
@@ -1309,7 +1309,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="54">
@@ -1885,7 +1885,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="86">
@@ -2173,7 +2173,7 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="102">
@@ -2893,7 +2893,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="142">
@@ -3145,7 +3145,7 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="156">
@@ -4099,7 +4099,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="209">
@@ -4225,7 +4225,7 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="216">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C250">
@@ -5665,7 +5665,7 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="296">
@@ -6097,7 +6097,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="320">
@@ -6475,7 +6475,7 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="341">
@@ -6691,7 +6691,7 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="353">
@@ -9067,7 +9067,7 @@
         <v>7</v>
       </c>
       <c r="D484">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="485">
@@ -9157,7 +9157,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="490">
@@ -9985,7 +9985,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="536">
@@ -10003,7 +10003,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="537">
@@ -10561,7 +10561,7 @@
         <v>7</v>
       </c>
       <c r="D567">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="568">
@@ -11731,7 +11731,7 @@
         <v>7</v>
       </c>
       <c r="D632">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="633">
@@ -12127,7 +12127,7 @@
         <v>7</v>
       </c>
       <c r="D654">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="655">
@@ -12235,7 +12235,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="661">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C661">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C662">
@@ -12613,7 +12613,7 @@
         <v>7</v>
       </c>
       <c r="D681">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="682">
@@ -12685,7 +12685,7 @@
         <v>7</v>
       </c>
       <c r="D685">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="686">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C691">
@@ -13243,7 +13243,7 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="717">
@@ -13513,7 +13513,7 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="732">
@@ -14737,7 +14737,7 @@
         <v>7</v>
       </c>
       <c r="D799">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="800">
@@ -15673,7 +15673,7 @@
         <v>7</v>
       </c>
       <c r="D851">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="852">
@@ -17239,7 +17239,7 @@
         <v>7</v>
       </c>
       <c r="D938">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="939">
@@ -17599,7 +17599,7 @@
         <v>7</v>
       </c>
       <c r="D958">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="959">
@@ -18625,7 +18625,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="1016">
@@ -19075,7 +19075,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="1041">
@@ -19183,7 +19183,7 @@
         <v>7</v>
       </c>
       <c r="D1046">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="1047">
@@ -20083,7 +20083,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="1097">
@@ -20101,7 +20101,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="1098">
@@ -20713,7 +20713,7 @@
         <v>7</v>
       </c>
       <c r="D1131">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="1132">
@@ -20785,7 +20785,7 @@
         <v>7</v>
       </c>
       <c r="D1135">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="1136">
@@ -21685,7 +21685,7 @@
         <v>7</v>
       </c>
       <c r="D1185">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="1186">
@@ -21721,7 +21721,7 @@
         <v>7</v>
       </c>
       <c r="D1187">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="1188">
@@ -21865,7 +21865,7 @@
         <v>7</v>
       </c>
       <c r="D1195">
-        <v>0.0009401020682245501</v>
+        <v>0.00094010206822455</v>
       </c>
     </row>
     <row r="1196">
